--- a/outbound/3_EEE_Allocation_Jakarta_202606.xlsx
+++ b/outbound/3_EEE_Allocation_Jakarta_202606.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -504,15 +504,8 @@
           <t>합계 : GW</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>열 레이블</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>102.602</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>10.2625</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -570,15 +563,15 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126011536</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -597,10 +590,10 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="5">
@@ -611,15 +604,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126011536</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -638,10 +631,10 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="6">
@@ -652,15 +645,15 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034273</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126010645</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -679,10 +672,10 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="7">
@@ -693,15 +686,15 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034273</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1125122363</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -720,10 +713,10 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="8">
@@ -734,15 +727,15 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034273</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1125122363</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -761,10 +754,10 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="9">
@@ -775,15 +768,15 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126011131</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -802,10 +795,10 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="10">
@@ -816,15 +809,15 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126011131</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -843,10 +836,10 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="11">
@@ -857,15 +850,15 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034273</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126010637</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -884,10 +877,10 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="12">
@@ -898,15 +891,15 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034273</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126010637</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -925,10 +918,10 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="13">
@@ -943,11 +936,11 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126011446</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -966,10 +959,10 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="14">
@@ -980,15 +973,15 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126011538</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1007,10 +1000,10 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="15">
@@ -1021,15 +1014,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126011213</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1048,10 +1041,10 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="16">
@@ -1062,15 +1055,15 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126011213</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1089,10 +1082,10 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="17">
@@ -1107,7 +1100,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -1130,10 +1123,10 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1141,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -1171,10 +1164,10 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="19">
@@ -1185,15 +1178,15 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034274</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126010933</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1212,10 +1205,10 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="20">
@@ -1230,11 +1223,11 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126010643</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1253,10 +1246,10 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="21">
@@ -1271,11 +1264,11 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126010643</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1294,10 +1287,10 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="22">
@@ -1308,15 +1301,15 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034274</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126010932</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1335,10 +1328,10 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="23">
@@ -1349,15 +1342,15 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2200034273</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126011132</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1376,10 +1369,10 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>5.13</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="24">
@@ -1390,7 +1383,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2200034275</t>
+          <t>2200034276</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
@@ -1398,7 +1391,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>1126011443</t>
+          <t>1126011536</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1439,7 +1432,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>1126010702</t>
+          <t>1126010645</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
